--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,8 +326,8 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegerinteger64markdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodeableReferenceCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioRatioRangeReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextAvailabilityExtendedContactDetailDosageMeta</t>
+    <t xml:space="preserve">string
+</t>
   </si>
   <si>
     <t>Value of extension</t>
@@ -340,6 +340,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t xml:space="preserve">ext-1
 </t>
   </si>
@@ -352,10 +355,6 @@
   </si>
   <si>
     <t>valueString</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
 </sst>
 </file>
@@ -678,7 +677,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1230,7 +1229,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>81</v>
@@ -1297,7 +1296,7 @@
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>99</v>
@@ -1309,28 +1308,28 @@
         <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>99</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>81</v>
@@ -1345,7 +1344,7 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>101</v>
@@ -1411,10 +1410,10 @@
         <v>81</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-vdasid.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
